--- a/Pipistrelli 2022.xlsx
+++ b/Pipistrelli 2022.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,7 +506,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Viale Margherita, 35</t>
@@ -546,10 +545,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44745</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -562,7 +560,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Via Brescia</t>
@@ -602,10 +599,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44754</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -618,7 +614,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Via San Giorgio</t>
@@ -658,10 +653,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44746</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -718,10 +712,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44747</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,10 +771,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -794,7 +786,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Via Porto</t>
@@ -834,7 +825,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Pipistrelli 2022.xlsx
+++ b/Pipistrelli 2022.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,6 +506,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Viale Margherita, 35</t>
@@ -522,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.5481426</v>
+        <v>45.5413</v>
       </c>
       <c r="I2" t="n">
-        <v>11.5548004</v>
+        <v>11.5517</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -545,9 +546,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44745</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,6 +562,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Via Brescia</t>
@@ -567,7 +570,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torri Di Quartesolo</t>
+          <t>Torri di Quartesolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -576,10 +579,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>45.5078361</v>
+        <v>45.5204</v>
       </c>
       <c r="I3" t="n">
-        <v>11.6242498</v>
+        <v>11.6214</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -599,9 +602,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44754</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -614,6 +618,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Via San Giorgio</t>
@@ -630,10 +635,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>45.7104304</v>
+        <v>45.6988</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5198978</v>
+        <v>11.5312</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -653,9 +658,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44746</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -689,10 +695,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45.5474967</v>
+        <v>45.5481</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5445382</v>
+        <v>11.5471</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -712,9 +718,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44747</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -748,10 +755,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.5460089</v>
+        <v>45.5434</v>
       </c>
       <c r="I6" t="n">
-        <v>11.570408</v>
+        <v>11.5645</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -771,9 +778,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44858</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,6 +794,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Via Porto</t>
@@ -802,10 +811,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45.6577546</v>
+        <v>45.6568</v>
       </c>
       <c r="I7" t="n">
-        <v>11.4092177</v>
+        <v>11.4111</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -825,6 +834,67 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Via Verona, 20</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pove del Grappa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>45.7958</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.7289</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>subadulto</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Fermo sul muro da 2 giorni, debilitato</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>liberato</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
